--- a/Result/profitability/2916.xlsx
+++ b/Result/profitability/2916.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.54</v>
       </c>
       <c r="M2" t="n">
-        <v>1.00125</v>
+        <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>52.60625</v>
+        <v>52.33374999999999</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.19</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9725</v>
+        <v>0.8462500000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>51.3525</v>
+        <v>51.22625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.09</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7337500000000001</v>
+        <v>0.68375</v>
       </c>
       <c r="N4" t="n">
-        <v>50.51125</v>
+        <v>50.52375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.24</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5525</v>
+        <v>0.5362500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>48.71625</v>
+        <v>48.57</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.31</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4737500000000001</v>
+        <v>0.5387500000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>46.405</v>
+        <v>46.2475</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.13</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4212500000000001</v>
+        <v>0.33125</v>
       </c>
       <c r="N7" t="n">
-        <v>44.39250000000001</v>
+        <v>44.22625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.25</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1987500000000001</v>
+        <v>0.1425000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>42.565</v>
+        <v>42.63125</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1648,7 +1648,7 @@
         <v>0.2050000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>41.77375</v>
+        <v>41.77375000000001</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
         <v>0.4175000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>42.35375</v>
+        <v>42.35375000000001</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2916</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>468</v>
+      </c>
+      <c r="D75" t="n">
+        <v>219</v>
+      </c>
+      <c r="E75" t="n">
+        <v>248</v>
+      </c>
+      <c r="F75" t="n">
+        <v>53.13</v>
+      </c>
+      <c r="G75" t="n">
+        <v>54</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>11.63%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>11</v>
+      </c>
+      <c r="J75" t="n">
+        <v>65</v>
+      </c>
+      <c r="K75" t="n">
+        <v>52</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.035</v>
+      </c>
+      <c r="N75" t="n">
+        <v>53.92</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.3571428571428571</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.5300000000000011</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.01007604562737652</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.1299999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.1382978723404255</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.169999999999995</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.02154696132596678</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
